--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N96_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N96_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.53073115357826</v>
+        <v>10.97374381245647</v>
       </c>
       <c r="D2" t="n">
-        <v>64.35124420684791</v>
+        <v>10.45707718361279</v>
       </c>
       <c r="E2" t="n">
-        <v>15.9401710775876</v>
+        <v>2.590277800107985</v>
       </c>
       <c r="F2" t="n">
-        <v>15.10746566821568</v>
+        <v>2.454963171085048</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.5007233751038</v>
+        <v>8.531367548454368</v>
       </c>
       <c r="D3" t="n">
-        <v>51.94664955199755</v>
+        <v>8.441330552199602</v>
       </c>
       <c r="E3" t="n">
-        <v>15.9401710775876</v>
+        <v>2.590277800107985</v>
       </c>
       <c r="F3" t="n">
-        <v>15.10746566821568</v>
+        <v>2.454963171085048</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.8071564454671</v>
+        <v>4.681162922388404</v>
       </c>
       <c r="D4" t="n">
-        <v>27.95533234406008</v>
+        <v>4.542741505909763</v>
       </c>
       <c r="E4" t="n">
-        <v>15.9401710775876</v>
+        <v>2.590277800107985</v>
       </c>
       <c r="F4" t="n">
-        <v>15.10746566821568</v>
+        <v>2.454963171085048</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
